--- a/RangeSayacv4.xlsx
+++ b/RangeSayacv4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaank\Downloads\IpekyolRangeSayac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF49274-D480-44D6-A484-1E86A0FC14F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80BB279-8B42-4684-A297-F156FDDAC53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CC9D8179-E951-433C-AC7D-5FB77520B83B}"/>
   </bookViews>
@@ -29216,7 +29216,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O567" xr:uid="{1CB84CC3-E4F8-433E-97ED-4BF62ECF93D3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>